--- a/Component catalogue.xlsx
+++ b/Component catalogue.xlsx
@@ -768,7 +768,8 @@
         <v>21</v>
       </c>
       <c r="G15" s="2">
-        <v>1153.8</v>
+        <f>1153.8+G14</f>
+        <v>1822.8</v>
       </c>
     </row>
     <row r="16">
@@ -791,7 +792,8 @@
         <v>22</v>
       </c>
       <c r="G16" s="2">
-        <v>3125.4</v>
+        <f>3125.4+G14</f>
+        <v>3794.4</v>
       </c>
     </row>
     <row r="17">
@@ -814,7 +816,8 @@
         <v>23</v>
       </c>
       <c r="G17" s="2">
-        <v>10709.0</v>
+        <f>10709+G14</f>
+        <v>11378</v>
       </c>
     </row>
     <row r="18">
